--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,1153 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131534185</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83227</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>311</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca phaeocephala</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>554918</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6587025</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131534164</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555119</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6586795</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131534161</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555007</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6587088</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131534197</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96331</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555006</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6587102</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131534193</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92405</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>554903</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6586957</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131534181</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79630</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555045</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6586787</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131534180</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79630</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>554981</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6587146</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131534162</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555045</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6586787</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131534189</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91776</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555043</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6587003</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131534188</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91776</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>555006</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6587102</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungsör</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På avbruten högstubbe.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534185</v>
+        <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>83227</v>
+        <v>75231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>311</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554918</v>
+        <v>555119</v>
       </c>
       <c r="R4" t="n">
-        <v>6587025</v>
+        <v>6586795</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +982,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534164</v>
+        <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>75228</v>
+        <v>83230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,26 +1025,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555119</v>
+        <v>554918</v>
       </c>
       <c r="R5" t="n">
-        <v>6586795</v>
+        <v>6587025</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75228</v>
+        <v>75231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96331</v>
+        <v>96334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>92405</v>
+        <v>79633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,34 +1360,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R8" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>79630</v>
+        <v>92408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,30 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R9" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79630</v>
+        <v>79633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75228</v>
+        <v>75231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91776</v>
+        <v>91779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91776</v>
+        <v>91779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>75231</v>
+        <v>75232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>83230</v>
+        <v>83231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75231</v>
+        <v>75232</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
+        <v>96335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75231</v>
+        <v>75232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>75232</v>
+        <v>75238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>83231</v>
+        <v>83237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75232</v>
+        <v>75238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96335</v>
+        <v>96341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79634</v>
+        <v>79640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79634</v>
+        <v>79640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75232</v>
+        <v>75238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91780</v>
+        <v>91786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91780</v>
+        <v>91786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534164</v>
+        <v>131534185</v>
       </c>
       <c r="B4" t="n">
-        <v>75238</v>
+        <v>83237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,26 +910,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555119</v>
+        <v>554918</v>
       </c>
       <c r="R4" t="n">
-        <v>6586795</v>
+        <v>6587025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534185</v>
+        <v>131534164</v>
       </c>
       <c r="B5" t="n">
-        <v>83237</v>
+        <v>75238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,30 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>311</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554918</v>
+        <v>555119</v>
       </c>
       <c r="R5" t="n">
-        <v>6587025</v>
+        <v>6586795</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B8" t="n">
-        <v>79640</v>
+        <v>92415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,30 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R8" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B9" t="n">
-        <v>92415</v>
+        <v>79640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1478,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R9" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>92415</v>
+        <v>79640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,34 +1360,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R8" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>79640</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,30 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R9" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534185</v>
+        <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>83237</v>
+        <v>75239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>311</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554918</v>
+        <v>555119</v>
       </c>
       <c r="R4" t="n">
-        <v>6587025</v>
+        <v>6586795</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +982,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534164</v>
+        <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>75238</v>
+        <v>83238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,26 +1025,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555119</v>
+        <v>554918</v>
       </c>
       <c r="R5" t="n">
-        <v>6586795</v>
+        <v>6587025</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96342</v>
+        <v>96343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79640</v>
+        <v>79641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79640</v>
+        <v>79641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91786</v>
+        <v>91787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>83238</v>
+        <v>83241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96343</v>
+        <v>96346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79641</v>
+        <v>79644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92417</v>
+        <v>92420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79641</v>
+        <v>79644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91787</v>
+        <v>91790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B8" t="n">
-        <v>79644</v>
+        <v>92420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,30 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R8" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B9" t="n">
-        <v>92420</v>
+        <v>79644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1478,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R9" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>92420</v>
+        <v>79644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,34 +1360,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R8" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>79644</v>
+        <v>92420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,30 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R9" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534164</v>
+        <v>131534185</v>
       </c>
       <c r="B4" t="n">
-        <v>75242</v>
+        <v>83243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,26 +910,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555119</v>
+        <v>554918</v>
       </c>
       <c r="R4" t="n">
-        <v>6586795</v>
+        <v>6587025</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,12 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534185</v>
+        <v>131534164</v>
       </c>
       <c r="B5" t="n">
-        <v>83241</v>
+        <v>75244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,30 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>311</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554918</v>
+        <v>555119</v>
       </c>
       <c r="R5" t="n">
-        <v>6587025</v>
+        <v>6586795</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75242</v>
+        <v>75244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96346</v>
+        <v>96352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79644</v>
+        <v>79646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92420</v>
+        <v>92426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79644</v>
+        <v>79646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75242</v>
+        <v>75244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91790</v>
+        <v>91796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91790</v>
+        <v>91796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>131534185</v>
       </c>
       <c r="B4" t="n">
-        <v>83243</v>
+        <v>83246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131534164</v>
       </c>
       <c r="B5" t="n">
-        <v>75244</v>
+        <v>75247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75244</v>
+        <v>75247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>79646</v>
+        <v>79649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>92426</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79646</v>
+        <v>79649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75244</v>
+        <v>75247</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91796</v>
+        <v>91799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91796</v>
+        <v>91799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>131534185</v>
       </c>
       <c r="B4" t="n">
-        <v>83246</v>
+        <v>83251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131534164</v>
       </c>
       <c r="B5" t="n">
-        <v>75247</v>
+        <v>75252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75247</v>
+        <v>75252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96355</v>
+        <v>96360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>92434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,30 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R8" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>79654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1478,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R9" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79649</v>
+        <v>79654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75247</v>
+        <v>75252</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91799</v>
+        <v>91804</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91799</v>
+        <v>91804</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534185</v>
+        <v>131534164</v>
       </c>
       <c r="B4" t="n">
-        <v>83251</v>
+        <v>75254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,30 +910,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>311</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554918</v>
+        <v>555119</v>
       </c>
       <c r="R4" t="n">
-        <v>6587025</v>
+        <v>6586795</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +982,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534164</v>
+        <v>131534185</v>
       </c>
       <c r="B5" t="n">
-        <v>75252</v>
+        <v>83253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,26 +1025,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555119</v>
+        <v>554918</v>
       </c>
       <c r="R5" t="n">
-        <v>6586795</v>
+        <v>6587025</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>131534161</v>
       </c>
       <c r="B6" t="n">
-        <v>75252</v>
+        <v>75254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>131534197</v>
       </c>
       <c r="B7" t="n">
-        <v>96360</v>
+        <v>96362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>131534193</v>
       </c>
       <c r="B8" t="n">
-        <v>92434</v>
+        <v>92436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>131534181</v>
       </c>
       <c r="B9" t="n">
-        <v>79654</v>
+        <v>79656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131534180</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>79656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>131534162</v>
       </c>
       <c r="B11" t="n">
-        <v>75252</v>
+        <v>75254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131534189</v>
       </c>
       <c r="B12" t="n">
-        <v>91804</v>
+        <v>91806</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>131534188</v>
       </c>
       <c r="B13" t="n">
-        <v>91804</v>
+        <v>91806</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B8" t="n">
-        <v>92436</v>
+        <v>79656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,34 +1360,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1391,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R8" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B9" t="n">
-        <v>79656</v>
+        <v>92436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,30 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R9" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534181</v>
+        <v>131534193</v>
       </c>
       <c r="B8" t="n">
-        <v>79656</v>
+        <v>92436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,30 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6431</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555045</v>
+        <v>554903</v>
       </c>
       <c r="R8" t="n">
-        <v>6586787</v>
+        <v>6586957</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534193</v>
+        <v>131534181</v>
       </c>
       <c r="B9" t="n">
-        <v>92436</v>
+        <v>79656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1478,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3884</v>
+        <v>6431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1509,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554903</v>
+        <v>555045</v>
       </c>
       <c r="R9" t="n">
-        <v>6586957</v>
+        <v>6586787</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78048345</v>
+        <v>131534185</v>
       </c>
       <c r="B2" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5445</v>
+        <v>311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Skäret NR, Vstm</t>
+          <t>Aspa, Kungs-Barkarö, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554993.1807238702</v>
+        <v>554918</v>
       </c>
       <c r="R2" t="n">
-        <v>6587112.187564466</v>
+        <v>6587025</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +782,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Karin Sandberg, Julia Carlsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +792,7 @@
         <v>78048347</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555000.0170093141</v>
+        <v>555000</v>
       </c>
       <c r="R3" t="n">
-        <v>6587062.913452945</v>
+        <v>6587063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +857,9 @@
           <t>2019-03-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-03-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,17 +879,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Karin Sandberg, Julia Carlsson</t>
+          <t>Karin Sandberg, Jacob Rudhe, Julia Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131534164</v>
+        <v>131534197</v>
       </c>
       <c r="B4" t="n">
-        <v>75254</v>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,26 +897,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555119</v>
+        <v>555006</v>
       </c>
       <c r="R4" t="n">
-        <v>6586795</v>
+        <v>6587102</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,7 +960,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,12 +970,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera ekar.</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131534185</v>
+        <v>131534193</v>
       </c>
       <c r="B5" t="n">
-        <v>83253</v>
+        <v>92497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,30 +1008,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>311</v>
+        <v>3884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554918</v>
+        <v>554903</v>
       </c>
       <c r="R5" t="n">
-        <v>6587025</v>
+        <v>6586957</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,51 +1115,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131534161</v>
+        <v>78048345</v>
       </c>
       <c r="B6" t="n">
-        <v>75254</v>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Aspa, Kungs-Barkarö, Vstm</t>
+          <t>NO Skäret NR, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555007</v>
+        <v>554993</v>
       </c>
       <c r="R6" t="n">
-        <v>6587088</v>
+        <v>6587112</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,22 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:46</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,45 +1205,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Karin Sandberg, Jacob Rudhe, Julia Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131534197</v>
+        <v>131534188</v>
       </c>
       <c r="B7" t="n">
-        <v>96362</v>
+        <v>91867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>5445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1312,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1303,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På avbruten högstubbe.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,37 +1335,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131534193</v>
+        <v>131534189</v>
       </c>
       <c r="B8" t="n">
-        <v>92436</v>
+        <v>91867</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3884</v>
+        <v>5445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1395,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554903</v>
+        <v>555043</v>
       </c>
       <c r="R8" t="n">
-        <v>6586957</v>
+        <v>6587003</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1430,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131534181</v>
+        <v>131534161</v>
       </c>
       <c r="B9" t="n">
-        <v>79656</v>
+        <v>75300</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,30 +1464,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6431</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,13 +1491,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>555045</v>
+        <v>555007</v>
       </c>
       <c r="R9" t="n">
-        <v>6586787</v>
+        <v>6587088</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131534180</v>
+        <v>131534162</v>
       </c>
       <c r="B10" t="n">
-        <v>79656</v>
+        <v>75300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,30 +1574,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6431</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1623,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554981</v>
+        <v>555045</v>
       </c>
       <c r="R10" t="n">
-        <v>6587146</v>
+        <v>6586787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1646,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131534162</v>
+        <v>131534164</v>
       </c>
       <c r="B11" t="n">
-        <v>75254</v>
+        <v>75300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,13 +1711,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555045</v>
+        <v>555119</v>
       </c>
       <c r="R11" t="n">
-        <v>6586787</v>
+        <v>6586795</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1756,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På flera ekar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,45 +1788,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131534189</v>
+        <v>131534180</v>
       </c>
       <c r="B12" t="n">
-        <v>91806</v>
+        <v>79707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1851,13 +1830,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555043</v>
+        <v>554981</v>
       </c>
       <c r="R12" t="n">
-        <v>6587003</v>
+        <v>6587146</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1896,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,45 +1902,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131534188</v>
+        <v>131534181</v>
       </c>
       <c r="B13" t="n">
-        <v>91806</v>
+        <v>79707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5445</v>
+        <v>6431</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1969,13 +1944,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555006</v>
+        <v>555045</v>
       </c>
       <c r="R13" t="n">
-        <v>6587102</v>
+        <v>6586787</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,12 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På avbruten högstubbe.</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 59332-2022 artfynd.xlsx
+++ b/artfynd/A 59332-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78048347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534197</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78048345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534189</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534161</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534162</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534164</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,6 +1954,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534180</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,8 +2073,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131534181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>